--- a/release_1_0_0/data/files/output/sim_v2/eval_sim_v2_loo.xlsx
+++ b/release_1_0_0/data/files/output/sim_v2/eval_sim_v2_loo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,7 +548,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>sim_v2</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -561,46 +561,46 @@
         <v>3432.306971428518</v>
       </c>
       <c r="G2" t="n">
-        <v>12653.45268433466</v>
+        <v>10738.49924213908</v>
       </c>
       <c r="H2" t="n">
-        <v>9221.145712906147</v>
+        <v>7306.192270710562</v>
       </c>
       <c r="I2" t="n">
-        <v>9221.145712906147</v>
+        <v>7306.192270710562</v>
       </c>
       <c r="J2" t="n">
-        <v>2.686573721309178</v>
+        <v>2.12865350667331</v>
       </c>
       <c r="K2" t="n">
         <v>1977.989434346401</v>
       </c>
       <c r="L2" t="n">
-        <v>6541.610912290459</v>
+        <v>5550.20024950137</v>
       </c>
       <c r="M2" t="n">
-        <v>4563.621477944058</v>
+        <v>3572.210815154969</v>
       </c>
       <c r="N2" t="n">
-        <v>4563.621477944058</v>
+        <v>3572.210815154969</v>
       </c>
       <c r="O2" t="n">
-        <v>2.307202151184413</v>
+        <v>1.805980736360888</v>
       </c>
       <c r="P2" t="n">
         <v>2214.074874999865</v>
       </c>
       <c r="Q2" t="n">
-        <v>6763.62324089858</v>
+        <v>5738.392028833131</v>
       </c>
       <c r="R2" t="n">
-        <v>4549.548365898714</v>
+        <v>3524.317153833266</v>
       </c>
       <c r="S2" t="n">
-        <v>4549.548365898714</v>
+        <v>3524.317153833266</v>
       </c>
       <c r="T2" t="n">
-        <v>2.054830402200825</v>
+        <v>1.591778667301611</v>
       </c>
       <c r="U2" t="n">
         <v>9</v>
@@ -615,72 +615,72 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H0373</t>
+          <t>H2075</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>connected</t>
+          <t>simply</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>sim_v2</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14139.8</v>
+        <v>4815.828</v>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>3432.306971428518</v>
+        <v>570.2660606060817</v>
       </c>
       <c r="G3" t="n">
-        <v>10738.49924213908</v>
+        <v>1993.296293710695</v>
       </c>
       <c r="H3" t="n">
-        <v>7306.192270710562</v>
+        <v>1423.030233104613</v>
       </c>
       <c r="I3" t="n">
-        <v>7306.192270710562</v>
+        <v>1423.030233104613</v>
       </c>
       <c r="J3" t="n">
-        <v>2.12865350667331</v>
+        <v>2.495379492849723</v>
       </c>
       <c r="K3" t="n">
-        <v>1977.989434346401</v>
+        <v>248.7434418642236</v>
       </c>
       <c r="L3" t="n">
-        <v>5550.20024950137</v>
+        <v>1115.053900402543</v>
       </c>
       <c r="M3" t="n">
-        <v>3572.210815154969</v>
+        <v>866.310458538319</v>
       </c>
       <c r="N3" t="n">
-        <v>3572.210815154969</v>
+        <v>866.310458538319</v>
       </c>
       <c r="O3" t="n">
-        <v>1.805980736360888</v>
+        <v>3.48274693011281</v>
       </c>
       <c r="P3" t="n">
-        <v>2214.074874999865</v>
+        <v>233.321212121201</v>
       </c>
       <c r="Q3" t="n">
-        <v>5738.392028833131</v>
+        <v>947.8373290228487</v>
       </c>
       <c r="R3" t="n">
-        <v>3524.317153833266</v>
+        <v>714.5161169016477</v>
       </c>
       <c r="S3" t="n">
-        <v>3524.317153833266</v>
+        <v>714.5161169016477</v>
       </c>
       <c r="T3" t="n">
-        <v>1.591778667301611</v>
+        <v>3.062371013787144</v>
       </c>
       <c r="U3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
         <v>2</v>
@@ -692,72 +692,72 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H2075</t>
+          <t>H3546</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>simply</t>
+          <t>connected</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>sim_v2</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4815.828</v>
+        <v>33554.88</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>570.2660606060817</v>
+        <v>17096.63041667935</v>
       </c>
       <c r="G4" t="n">
-        <v>1999.086899193752</v>
+        <v>9949.347210553828</v>
       </c>
       <c r="H4" t="n">
-        <v>1428.82083858767</v>
+        <v>-7147.283206125525</v>
       </c>
       <c r="I4" t="n">
-        <v>1428.82083858767</v>
+        <v>7147.283206125525</v>
       </c>
       <c r="J4" t="n">
-        <v>2.505533710123152</v>
+        <v>0.4180521560057054</v>
       </c>
       <c r="K4" t="n">
-        <v>248.7434418642236</v>
+        <v>8864.534661573482</v>
       </c>
       <c r="L4" t="n">
-        <v>1118.293048137287</v>
+        <v>5735.546625177109</v>
       </c>
       <c r="M4" t="n">
-        <v>869.549606273063</v>
+        <v>-3128.988036396373</v>
       </c>
       <c r="N4" t="n">
-        <v>869.549606273063</v>
+        <v>3128.988036396373</v>
       </c>
       <c r="O4" t="n">
-        <v>3.495768972866854</v>
+        <v>0.3529782617874008</v>
       </c>
       <c r="P4" t="n">
-        <v>233.321212121201</v>
+        <v>9167.626249997114</v>
       </c>
       <c r="Q4" t="n">
-        <v>951.493641990569</v>
+        <v>6471.286683364962</v>
       </c>
       <c r="R4" t="n">
-        <v>718.172429869368</v>
+        <v>-2696.339566632152</v>
       </c>
       <c r="S4" t="n">
-        <v>718.172429869368</v>
+        <v>2696.339566632152</v>
       </c>
       <c r="T4" t="n">
-        <v>3.078041740569675</v>
+        <v>0.2941153460126061</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V4" t="n">
         <v>2</v>
@@ -769,72 +769,72 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H2075</t>
+          <t>H6188</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>simply</t>
+          <t>liberty</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>sim_v2</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4815.828</v>
+        <v>8505.23</v>
       </c>
       <c r="E5" t="n">
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>570.2660606060817</v>
+        <v>1438.426056822751</v>
       </c>
       <c r="G5" t="n">
-        <v>1993.296293710695</v>
+        <v>1515.226734659087</v>
       </c>
       <c r="H5" t="n">
-        <v>1423.030233104613</v>
+        <v>76.80067783633604</v>
       </c>
       <c r="I5" t="n">
-        <v>1423.030233104613</v>
+        <v>76.80067783633604</v>
       </c>
       <c r="J5" t="n">
-        <v>2.495379492849723</v>
+        <v>0.05339216254603746</v>
       </c>
       <c r="K5" t="n">
-        <v>248.7434418642236</v>
+        <v>795.1738730737154</v>
       </c>
       <c r="L5" t="n">
-        <v>1115.053900402543</v>
+        <v>691.3281133614805</v>
       </c>
       <c r="M5" t="n">
-        <v>866.310458538319</v>
+        <v>-103.8457597122349</v>
       </c>
       <c r="N5" t="n">
-        <v>866.310458538319</v>
+        <v>103.8457597122349</v>
       </c>
       <c r="O5" t="n">
-        <v>3.48274693011281</v>
+        <v>0.1305950349083062</v>
       </c>
       <c r="P5" t="n">
-        <v>233.321212121201</v>
+        <v>750.5261190476397</v>
       </c>
       <c r="Q5" t="n">
-        <v>947.8373290228487</v>
+        <v>838.0128820978642</v>
       </c>
       <c r="R5" t="n">
-        <v>714.5161169016477</v>
+        <v>87.48676305022457</v>
       </c>
       <c r="S5" t="n">
-        <v>714.5161169016477</v>
+        <v>87.48676305022457</v>
       </c>
       <c r="T5" t="n">
-        <v>3.062371013787144</v>
+        <v>0.116567246402082</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
@@ -846,72 +846,72 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H3546</t>
+          <t>HB5I0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>connected</t>
+          <t>liberty</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>sim_v2</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>33554.88</v>
+        <v>18841.68</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>17096.63041667935</v>
+        <v>1766.508730769235</v>
       </c>
       <c r="G6" t="n">
-        <v>9949.347210553828</v>
+        <v>2175.113223112842</v>
       </c>
       <c r="H6" t="n">
-        <v>-7147.283206125525</v>
+        <v>408.604492343607</v>
       </c>
       <c r="I6" t="n">
-        <v>7147.283206125525</v>
+        <v>408.604492343607</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4180521560057054</v>
+        <v>0.2313062399446383</v>
       </c>
       <c r="K6" t="n">
-        <v>8864.534661573482</v>
+        <v>815.1594794547862</v>
       </c>
       <c r="L6" t="n">
-        <v>5735.546625177109</v>
+        <v>1202.322496184466</v>
       </c>
       <c r="M6" t="n">
-        <v>-3128.988036396373</v>
+        <v>387.1630167296796</v>
       </c>
       <c r="N6" t="n">
-        <v>3128.988036396373</v>
+        <v>387.1630167296796</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3529782617874008</v>
+        <v>0.4749537072041792</v>
       </c>
       <c r="P6" t="n">
-        <v>9167.626249997114</v>
+        <v>974.3293076923151</v>
       </c>
       <c r="Q6" t="n">
-        <v>6471.286683364962</v>
+        <v>1150.076693968492</v>
       </c>
       <c r="R6" t="n">
-        <v>-2696.339566632152</v>
+        <v>175.7473862761765</v>
       </c>
       <c r="S6" t="n">
-        <v>2696.339566632152</v>
+        <v>175.7473862761765</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2941153460126061</v>
+        <v>0.1803778095235908</v>
       </c>
       <c r="U6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V6" t="n">
         <v>2</v>
@@ -923,637 +923,77 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H3546</t>
+          <t>HB6A3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>connected</t>
+          <t>simply</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>sim_v2</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33554.88</v>
+        <v>3520.614999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>17096.63041667935</v>
+        <v>1085.428421052641</v>
       </c>
       <c r="G7" t="n">
-        <v>9857.239904792235</v>
+        <v>422.4384616734756</v>
       </c>
       <c r="H7" t="n">
-        <v>-7239.390511887117</v>
+        <v>-662.9899593791652</v>
       </c>
       <c r="I7" t="n">
-        <v>7239.390511887117</v>
+        <v>662.9899593791652</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4234396097621914</v>
+        <v>0.6108094707306468</v>
       </c>
       <c r="K7" t="n">
-        <v>8864.534661573482</v>
+        <v>607.1911078395337</v>
       </c>
       <c r="L7" t="n">
-        <v>5682.234220275579</v>
+        <v>180.006045991362</v>
       </c>
       <c r="M7" t="n">
-        <v>-3182.300441297903</v>
+        <v>-427.1850618481718</v>
       </c>
       <c r="N7" t="n">
-        <v>3182.300441297903</v>
+        <v>427.1850618481718</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3589923851381314</v>
+        <v>0.7035430136125556</v>
       </c>
       <c r="P7" t="n">
-        <v>9167.626249997114</v>
+        <v>522.3989473684123</v>
       </c>
       <c r="Q7" t="n">
-        <v>6407.651299446268</v>
+        <v>171.714378819114</v>
       </c>
       <c r="R7" t="n">
-        <v>-2759.974950550846</v>
+        <v>-350.6845685492983</v>
       </c>
       <c r="S7" t="n">
-        <v>2759.974950550846</v>
+        <v>350.6845685492983</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3010566612651465</v>
+        <v>0.6712964685627217</v>
       </c>
       <c r="U7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="V7" t="n">
         <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>H5586</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>connected</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="n">
-        <v>8</v>
-      </c>
-      <c r="V8" t="n">
-        <v>2</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>H5586</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>connected</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="n">
-        <v>8</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>H6188</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>liberty</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>8505.23</v>
-      </c>
-      <c r="E10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1438.426056822751</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1460.258841858444</v>
-      </c>
-      <c r="H10" t="n">
-        <v>21.83278503569318</v>
-      </c>
-      <c r="I10" t="n">
-        <v>21.83278503569318</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.01517824634233771</v>
-      </c>
-      <c r="K10" t="n">
-        <v>795.1738730737154</v>
-      </c>
-      <c r="L10" t="n">
-        <v>666.4944243929524</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-128.679448680763</v>
-      </c>
-      <c r="N10" t="n">
-        <v>128.679448680763</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.1618255491511024</v>
-      </c>
-      <c r="P10" t="n">
-        <v>750.5261190476397</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>805.7633654708274</v>
-      </c>
-      <c r="R10" t="n">
-        <v>55.23724642318768</v>
-      </c>
-      <c r="S10" t="n">
-        <v>55.23724642318768</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.07359803346121989</v>
-      </c>
-      <c r="U10" t="n">
-        <v>5</v>
-      </c>
-      <c r="V10" t="n">
-        <v>2</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>H6188</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>liberty</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>8505.23</v>
-      </c>
-      <c r="E11" t="n">
-        <v>6</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1438.426056822751</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1515.226734659087</v>
-      </c>
-      <c r="H11" t="n">
-        <v>76.80067783633604</v>
-      </c>
-      <c r="I11" t="n">
-        <v>76.80067783633604</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.05339216254603746</v>
-      </c>
-      <c r="K11" t="n">
-        <v>795.1738730737154</v>
-      </c>
-      <c r="L11" t="n">
-        <v>691.3281133614805</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-103.8457597122349</v>
-      </c>
-      <c r="N11" t="n">
-        <v>103.8457597122349</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.1305950349083062</v>
-      </c>
-      <c r="P11" t="n">
-        <v>750.5261190476397</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>838.0128820978642</v>
-      </c>
-      <c r="R11" t="n">
-        <v>87.48676305022457</v>
-      </c>
-      <c r="S11" t="n">
-        <v>87.48676305022457</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.116567246402082</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>HB5I0</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>liberty</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>18841.68</v>
-      </c>
-      <c r="E12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1766.508730769235</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2329.589714008292</v>
-      </c>
-      <c r="H12" t="n">
-        <v>563.0809832390569</v>
-      </c>
-      <c r="I12" t="n">
-        <v>563.0809832390569</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.3187535806821971</v>
-      </c>
-      <c r="K12" t="n">
-        <v>815.1594794547862</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1287.639040375007</v>
-      </c>
-      <c r="M12" t="n">
-        <v>472.4795609202204</v>
-      </c>
-      <c r="N12" t="n">
-        <v>472.4795609202204</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.5796161031412345</v>
-      </c>
-      <c r="P12" t="n">
-        <v>974.3293076923151</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1230.782937520174</v>
-      </c>
-      <c r="R12" t="n">
-        <v>256.453629827859</v>
-      </c>
-      <c r="S12" t="n">
-        <v>256.453629827859</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.2632104236249095</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>2</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>HB5I0</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>liberty</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>18841.68</v>
-      </c>
-      <c r="E13" t="n">
-        <v>8</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1766.508730769235</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2175.113223112842</v>
-      </c>
-      <c r="H13" t="n">
-        <v>408.604492343607</v>
-      </c>
-      <c r="I13" t="n">
-        <v>408.604492343607</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.2313062399446383</v>
-      </c>
-      <c r="K13" t="n">
-        <v>815.1594794547862</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1202.322496184466</v>
-      </c>
-      <c r="M13" t="n">
-        <v>387.1630167296796</v>
-      </c>
-      <c r="N13" t="n">
-        <v>387.1630167296796</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.4749537072041792</v>
-      </c>
-      <c r="P13" t="n">
-        <v>974.3293076923151</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1150.076693968491</v>
-      </c>
-      <c r="R13" t="n">
-        <v>175.7473862761763</v>
-      </c>
-      <c r="S13" t="n">
-        <v>175.7473862761763</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.1803778095235906</v>
-      </c>
-      <c r="U13" t="n">
-        <v>5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>2</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>HB6A3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>simply</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>3520.614999999999</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1085.428421052641</v>
-      </c>
-      <c r="G14" t="n">
-        <v>442.0809767818756</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-643.3474442707651</v>
-      </c>
-      <c r="I14" t="n">
-        <v>643.3474442707651</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.5927129157414649</v>
-      </c>
-      <c r="K14" t="n">
-        <v>607.1911078395337</v>
-      </c>
-      <c r="L14" t="n">
-        <v>188.5456321875848</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-418.6454756519489</v>
-      </c>
-      <c r="N14" t="n">
-        <v>418.6454756519489</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.6894789305158715</v>
-      </c>
-      <c r="P14" t="n">
-        <v>522.3989473684123</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>179.7352683283283</v>
-      </c>
-      <c r="R14" t="n">
-        <v>-342.663679040084</v>
-      </c>
-      <c r="S14" t="n">
-        <v>342.663679040084</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.6559425143680979</v>
-      </c>
-      <c r="U14" t="n">
-        <v>4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>HB6A3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>simply</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>3520.614999999999</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1085.428421052641</v>
-      </c>
-      <c r="G15" t="n">
-        <v>422.4384616734756</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-662.9899593791652</v>
-      </c>
-      <c r="I15" t="n">
-        <v>662.9899593791652</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.6108094707306468</v>
-      </c>
-      <c r="K15" t="n">
-        <v>607.1911078395337</v>
-      </c>
-      <c r="L15" t="n">
-        <v>180.006045991362</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-427.1850618481718</v>
-      </c>
-      <c r="N15" t="n">
-        <v>427.1850618481718</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.7035430136125556</v>
-      </c>
-      <c r="P15" t="n">
-        <v>522.3989473684123</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>171.714378819114</v>
-      </c>
-      <c r="R15" t="n">
-        <v>-350.6845685492983</v>
-      </c>
-      <c r="S15" t="n">
-        <v>350.6845685492983</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.6712964685627217</v>
-      </c>
-      <c r="U15" t="n">
-        <v>4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>2</v>
-      </c>
-      <c r="W15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1568,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1641,7 +1081,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>sim_v2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1650,344 +1090,168 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>8230.268112396632</v>
+        <v>7226.737738418044</v>
       </c>
       <c r="E2" t="n">
-        <v>8289.701539930393</v>
+        <v>7227.174507549777</v>
       </c>
       <c r="F2" t="n">
-        <v>1.555006665535685</v>
+        <v>1.273352831339508</v>
       </c>
       <c r="G2" t="n">
-        <v>990.8776005095151</v>
+        <v>79.45453229251871</v>
       </c>
       <c r="H2" t="n">
-        <v>3872.96095962098</v>
+        <v>3350.599425775671</v>
       </c>
       <c r="I2" t="n">
-        <v>3934.061329760705</v>
+        <v>3357.920207496134</v>
       </c>
       <c r="J2" t="n">
-        <v>1.333097268161272</v>
+        <v>1.079479499074144</v>
       </c>
       <c r="K2" t="n">
-        <v>3654.76165822478</v>
+        <v>3110.328360232709</v>
       </c>
       <c r="L2" t="n">
-        <v>3762.70195878705</v>
+        <v>3137.758631522625</v>
       </c>
       <c r="M2" t="n">
-        <v>1.177943531732986</v>
+        <v>0.9429470066571085</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>sim_v2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>simply</t>
+          <t>liberty</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1043.010096241889</v>
+        <v>242.7025850899715</v>
       </c>
       <c r="E3" t="n">
-        <v>1110.083494735274</v>
+        <v>293.9863732211898</v>
       </c>
       <c r="F3" t="n">
-        <v>1.553094481790185</v>
+        <v>0.1423492012453379</v>
       </c>
       <c r="G3" t="n">
-        <v>380.0201368627241</v>
+        <v>242.7025850899715</v>
       </c>
       <c r="H3" t="n">
-        <v>646.7477601932454</v>
+        <v>245.5043882209573</v>
       </c>
       <c r="I3" t="n">
-        <v>683.0010569681057</v>
+        <v>283.4423603957579</v>
       </c>
       <c r="J3" t="n">
-        <v>2.093144971862683</v>
+        <v>0.3027743710562427</v>
       </c>
       <c r="K3" t="n">
-        <v>532.600342725473</v>
+        <v>131.6170746632005</v>
       </c>
       <c r="L3" t="n">
-        <v>562.8112240933085</v>
+        <v>138.8183660253818</v>
       </c>
       <c r="M3" t="n">
-        <v>1.866833741174933</v>
+        <v>0.1484725279628364</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>sim_v2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>liberty</t>
+          <t>simply</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>242.7025850899715</v>
+        <v>1043.010096241889</v>
       </c>
       <c r="E4" t="n">
-        <v>293.9863732211899</v>
+        <v>1110.083494735273</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1423492012453379</v>
+        <v>1.553094481790185</v>
       </c>
       <c r="G4" t="n">
-        <v>242.7025850899715</v>
+        <v>380.0201368627239</v>
       </c>
       <c r="H4" t="n">
-        <v>245.5043882209573</v>
+        <v>646.7477601932454</v>
       </c>
       <c r="I4" t="n">
-        <v>283.4423603957579</v>
+        <v>683.0010569681057</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3027743710562427</v>
+        <v>2.093144971862683</v>
       </c>
       <c r="K4" t="n">
-        <v>131.6170746632004</v>
+        <v>532.600342725473</v>
       </c>
       <c r="L4" t="n">
-        <v>138.8183660253816</v>
+        <v>562.8112240933085</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1484725279628363</v>
+        <v>1.866833741174933</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>simply</t>
-        </is>
-      </c>
+          <t>sim_v2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1036.084141429218</v>
+        <v>2837.483473249968</v>
       </c>
       <c r="E5" t="n">
-        <v>1108.021868654247</v>
+        <v>4224.956201567885</v>
       </c>
       <c r="F5" t="n">
-        <v>1.549123312932308</v>
+        <v>0.9895988381250103</v>
       </c>
       <c r="G5" t="n">
-        <v>392.7366971584525</v>
+        <v>234.0590847484048</v>
       </c>
       <c r="H5" t="n">
-        <v>644.0975409625059</v>
+        <v>1414.283858063291</v>
       </c>
       <c r="I5" t="n">
-        <v>682.415032093185</v>
+        <v>1985.149711851909</v>
       </c>
       <c r="J5" t="n">
-        <v>2.092623951691363</v>
+        <v>1.158466280664357</v>
       </c>
       <c r="K5" t="n">
-        <v>530.418054454726</v>
+        <v>1258.181925873794</v>
       </c>
       <c r="L5" t="n">
-        <v>562.6677687400256</v>
+        <v>1842.24104850642</v>
       </c>
       <c r="M5" t="n">
-        <v>1.866992127468887</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>liberty</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>292.456884137375</v>
-      </c>
-      <c r="E6" t="n">
-        <v>398.4575662400438</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.1669659135122674</v>
-      </c>
-      <c r="G6" t="n">
-        <v>292.456884137375</v>
-      </c>
-      <c r="H6" t="n">
-        <v>300.5795048004917</v>
-      </c>
-      <c r="I6" t="n">
-        <v>346.2624264919234</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.3707208261461684</v>
-      </c>
-      <c r="K6" t="n">
-        <v>155.8454381255233</v>
-      </c>
-      <c r="L6" t="n">
-        <v>185.4988108375637</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.1684042285430647</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>connected</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7226.737738418044</v>
-      </c>
-      <c r="E7" t="n">
-        <v>7227.174507549777</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.273352831339508</v>
-      </c>
-      <c r="G7" t="n">
-        <v>79.45453229251871</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3350.599425775671</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3357.920207496134</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.079479499074144</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3110.328360232709</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3137.758631522625</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.9429470066571084</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3186.269712654409</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4834.102209464005</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.090365297326753</v>
-      </c>
-      <c r="G8" t="n">
-        <v>558.6903939351141</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1605.879335127993</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2313.901934708656</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.265480681999601</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1447.008383601677</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2199.161268715942</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.071113295914979</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2837.483473249968</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4224.956201567885</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.9895988381250103</v>
-      </c>
-      <c r="G9" t="n">
-        <v>234.0590847484048</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1414.283858063291</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1985.149711851909</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.158466280664356</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1258.181925873794</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1842.24104850642</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.9860844252649591</v>
+        <v>0.9860844252649592</v>
       </c>
     </row>
   </sheetData>
@@ -2001,7 +1265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2012,149 +1276,104 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>solution</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>nombre_hotels</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>montant_ventes_mae</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>montant_ventes_rmse</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>montant_ventes_mape</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>montant_ventes_biais</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>marge_selon_coef_mae</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>marge_selon_coef_rmse</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>marge_selon_coef_mape</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>marge_mae</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>marge_rmse</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>marge_mape</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>rang_ca</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>rang_marge_selon_coef</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>rang_marge</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+          <t>sim_v2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
         <v>2837.483473249968</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>4224.956201567885</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>0.9895988381250103</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
+        <v>234.0590847484048</v>
+      </c>
+      <c r="H2" t="n">
         <v>1414.283858063291</v>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
         <v>1985.149711851909</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.158466280664356</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
+        <v>1.158466280664357</v>
+      </c>
+      <c r="K2" t="n">
         <v>1258.181925873794</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>1842.24104850642</v>
       </c>
-      <c r="J2" t="n">
-        <v>0.9860844252649591</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
       <c r="M2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3186.269712654409</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4834.102209464005</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.090365297326753</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1605.879335127993</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2313.901934708656</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.265480681999601</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1447.008383601677</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2199.161268715942</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.071113295914979</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
+        <v>0.9860844252649592</v>
       </c>
     </row>
   </sheetData>

--- a/release_1_0_0/data/files/output/sim_v2/eval_sim_v2_loo.xlsx
+++ b/release_1_0_0/data/files/output/sim_v2/eval_sim_v2_loo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,46 +561,46 @@
         <v>3432.306971428518</v>
       </c>
       <c r="G2" t="n">
-        <v>10738.49924213908</v>
+        <v>11563.90509922685</v>
       </c>
       <c r="H2" t="n">
-        <v>7306.192270710562</v>
+        <v>8131.598127798337</v>
       </c>
       <c r="I2" t="n">
-        <v>7306.192270710562</v>
+        <v>8131.598127798337</v>
       </c>
       <c r="J2" t="n">
-        <v>2.12865350667331</v>
+        <v>2.369134869196733</v>
       </c>
       <c r="K2" t="n">
         <v>1977.989434346401</v>
       </c>
       <c r="L2" t="n">
-        <v>5550.20024950137</v>
+        <v>6068.039785701236</v>
       </c>
       <c r="M2" t="n">
-        <v>3572.210815154969</v>
+        <v>4090.050351354835</v>
       </c>
       <c r="N2" t="n">
-        <v>3572.210815154969</v>
+        <v>4090.050351354835</v>
       </c>
       <c r="O2" t="n">
-        <v>1.805980736360888</v>
+        <v>2.067781698088966</v>
       </c>
       <c r="P2" t="n">
         <v>2214.074874999865</v>
       </c>
       <c r="Q2" t="n">
-        <v>5738.392028833131</v>
+        <v>6058.900290863949</v>
       </c>
       <c r="R2" t="n">
-        <v>3524.317153833266</v>
+        <v>3844.825415864083</v>
       </c>
       <c r="S2" t="n">
-        <v>3524.317153833266</v>
+        <v>3844.825415864083</v>
       </c>
       <c r="T2" t="n">
-        <v>1.591778667301611</v>
+        <v>1.736538117693205</v>
       </c>
       <c r="U2" t="n">
         <v>9</v>
@@ -609,7 +609,7 @@
         <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -638,49 +638,49 @@
         <v>570.2660606060817</v>
       </c>
       <c r="G3" t="n">
-        <v>1993.296293710695</v>
+        <v>638.5548036564379</v>
       </c>
       <c r="H3" t="n">
-        <v>1423.030233104613</v>
+        <v>68.28874305035617</v>
       </c>
       <c r="I3" t="n">
-        <v>1423.030233104613</v>
+        <v>68.28874305035617</v>
       </c>
       <c r="J3" t="n">
-        <v>2.495379492849723</v>
+        <v>0.1197489168087235</v>
       </c>
       <c r="K3" t="n">
         <v>248.7434418642236</v>
       </c>
       <c r="L3" t="n">
-        <v>1115.053900402543</v>
+        <v>274.8754279611125</v>
       </c>
       <c r="M3" t="n">
-        <v>866.310458538319</v>
+        <v>26.13198609688882</v>
       </c>
       <c r="N3" t="n">
-        <v>866.310458538319</v>
+        <v>26.13198609688882</v>
       </c>
       <c r="O3" t="n">
-        <v>3.48274693011281</v>
+        <v>0.1050559801739535</v>
       </c>
       <c r="P3" t="n">
         <v>233.321212121201</v>
       </c>
       <c r="Q3" t="n">
-        <v>947.8373290228487</v>
+        <v>260.0828622855092</v>
       </c>
       <c r="R3" t="n">
-        <v>714.5161169016477</v>
+        <v>26.76165016430821</v>
       </c>
       <c r="S3" t="n">
-        <v>714.5161169016477</v>
+        <v>26.76165016430821</v>
       </c>
       <c r="T3" t="n">
-        <v>3.062371013787144</v>
+        <v>0.1146987447948222</v>
       </c>
       <c r="U3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="V3" t="n">
         <v>2</v>
@@ -715,46 +715,46 @@
         <v>17096.63041667935</v>
       </c>
       <c r="G4" t="n">
-        <v>9949.347210553828</v>
+        <v>13869.445661997</v>
       </c>
       <c r="H4" t="n">
-        <v>-7147.283206125525</v>
+        <v>-3227.184754682352</v>
       </c>
       <c r="I4" t="n">
-        <v>7147.283206125525</v>
+        <v>3227.184754682352</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4180521560057054</v>
+        <v>0.1887614504162138</v>
       </c>
       <c r="K4" t="n">
         <v>8864.534661573482</v>
       </c>
       <c r="L4" t="n">
-        <v>5735.546625177109</v>
+        <v>7873.942033712021</v>
       </c>
       <c r="M4" t="n">
-        <v>-3128.988036396373</v>
+        <v>-990.5926278614606</v>
       </c>
       <c r="N4" t="n">
-        <v>3128.988036396373</v>
+        <v>990.5926278614606</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3529782617874008</v>
+        <v>0.1117478430261592</v>
       </c>
       <c r="P4" t="n">
         <v>9167.626249997114</v>
       </c>
       <c r="Q4" t="n">
-        <v>6471.286683364962</v>
+        <v>7771.045887174265</v>
       </c>
       <c r="R4" t="n">
-        <v>-2696.339566632152</v>
+        <v>-1396.58036282285</v>
       </c>
       <c r="S4" t="n">
-        <v>2696.339566632152</v>
+        <v>1396.58036282285</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2941153460126061</v>
+        <v>0.1523382743513665</v>
       </c>
       <c r="U4" t="n">
         <v>9</v>
@@ -763,13 +763,13 @@
         <v>2</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H6188</t>
+          <t>HB5I0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -783,75 +783,75 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8505.23</v>
+        <v>18841.68</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>1438.426056822751</v>
+        <v>1766.508730769235</v>
       </c>
       <c r="G5" t="n">
-        <v>1515.226734659087</v>
+        <v>1995.706269346929</v>
       </c>
       <c r="H5" t="n">
-        <v>76.80067783633604</v>
+        <v>229.1975385776941</v>
       </c>
       <c r="I5" t="n">
-        <v>76.80067783633604</v>
+        <v>229.1975385776941</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05339216254603746</v>
+        <v>0.1297460547946961</v>
       </c>
       <c r="K5" t="n">
-        <v>795.1738730737154</v>
+        <v>815.1594794547862</v>
       </c>
       <c r="L5" t="n">
-        <v>691.3281133614805</v>
+        <v>959.7891359706011</v>
       </c>
       <c r="M5" t="n">
-        <v>-103.8457597122349</v>
+        <v>144.629656515815</v>
       </c>
       <c r="N5" t="n">
-        <v>103.8457597122349</v>
+        <v>144.629656515815</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1305950349083062</v>
+        <v>0.1774249826703231</v>
       </c>
       <c r="P5" t="n">
-        <v>750.5261190476397</v>
+        <v>974.3293076923151</v>
       </c>
       <c r="Q5" t="n">
-        <v>838.0128820978642</v>
+        <v>1093.583211466244</v>
       </c>
       <c r="R5" t="n">
-        <v>87.48676305022457</v>
+        <v>119.2539037739289</v>
       </c>
       <c r="S5" t="n">
-        <v>87.48676305022457</v>
+        <v>119.2539037739289</v>
       </c>
       <c r="T5" t="n">
-        <v>0.116567246402082</v>
+        <v>0.1223958910323451</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HB5I0</t>
+          <t>HB6A3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>liberty</t>
+          <t>connected</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -860,141 +860,64 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18841.68</v>
+        <v>3520.614999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>1766.508730769235</v>
+        <v>1085.428421052641</v>
       </c>
       <c r="G6" t="n">
-        <v>2175.113223112842</v>
+        <v>653.2037691736537</v>
       </c>
       <c r="H6" t="n">
-        <v>408.604492343607</v>
+        <v>-432.2246518789871</v>
       </c>
       <c r="I6" t="n">
-        <v>408.604492343607</v>
+        <v>432.2246518789871</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2313062399446383</v>
+        <v>0.3982064993837352</v>
       </c>
       <c r="K6" t="n">
-        <v>815.1594794547862</v>
+        <v>607.1911078395337</v>
       </c>
       <c r="L6" t="n">
-        <v>1202.322496184466</v>
+        <v>353.4275239598608</v>
       </c>
       <c r="M6" t="n">
-        <v>387.1630167296796</v>
+        <v>-253.763583879673</v>
       </c>
       <c r="N6" t="n">
-        <v>387.1630167296796</v>
+        <v>253.763583879673</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4749537072041792</v>
+        <v>0.4179303362702352</v>
       </c>
       <c r="P6" t="n">
-        <v>974.3293076923151</v>
+        <v>522.3989473684123</v>
       </c>
       <c r="Q6" t="n">
-        <v>1150.076693968492</v>
+        <v>380.8691424092727</v>
       </c>
       <c r="R6" t="n">
-        <v>175.7473862761765</v>
+        <v>-141.5298049591396</v>
       </c>
       <c r="S6" t="n">
-        <v>175.7473862761765</v>
+        <v>141.5298049591396</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1803778095235908</v>
+        <v>0.2709228371766383</v>
       </c>
       <c r="U6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V6" t="n">
         <v>2</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>HB6A3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>simply</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>sim_v2</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>3520.614999999999</v>
-      </c>
-      <c r="E7" t="n">
         <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1085.428421052641</v>
-      </c>
-      <c r="G7" t="n">
-        <v>422.4384616734756</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-662.9899593791652</v>
-      </c>
-      <c r="I7" t="n">
-        <v>662.9899593791652</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.6108094707306468</v>
-      </c>
-      <c r="K7" t="n">
-        <v>607.1911078395337</v>
-      </c>
-      <c r="L7" t="n">
-        <v>180.006045991362</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-427.1850618481718</v>
-      </c>
-      <c r="N7" t="n">
-        <v>427.1850618481718</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.7035430136125556</v>
-      </c>
-      <c r="P7" t="n">
-        <v>522.3989473684123</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>171.714378819114</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-350.6845685492983</v>
-      </c>
-      <c r="S7" t="n">
-        <v>350.6845685492983</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.6712964685627217</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" t="n">
-        <v>2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1086,41 +1009,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>connected</t>
+          <t>simply</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7226.737738418044</v>
+        <v>68.28874305035617</v>
       </c>
       <c r="E2" t="n">
-        <v>7227.174507549777</v>
+        <v>68.28874305035617</v>
       </c>
       <c r="F2" t="n">
-        <v>1.273352831339508</v>
+        <v>0.1197489168087235</v>
       </c>
       <c r="G2" t="n">
-        <v>79.45453229251871</v>
+        <v>68.28874305035617</v>
       </c>
       <c r="H2" t="n">
-        <v>3350.599425775671</v>
+        <v>26.13198609688882</v>
       </c>
       <c r="I2" t="n">
-        <v>3357.920207496134</v>
+        <v>26.13198609688882</v>
       </c>
       <c r="J2" t="n">
-        <v>1.079479499074144</v>
+        <v>0.1050559801739535</v>
       </c>
       <c r="K2" t="n">
-        <v>3110.328360232709</v>
+        <v>26.76165016430821</v>
       </c>
       <c r="L2" t="n">
-        <v>3137.758631522625</v>
+        <v>26.76165016430821</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9429470066571085</v>
+        <v>0.1146987447948222</v>
       </c>
     </row>
     <row r="3">
@@ -1135,37 +1058,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>242.7025850899715</v>
+        <v>229.1975385776941</v>
       </c>
       <c r="E3" t="n">
-        <v>293.9863732211898</v>
+        <v>229.1975385776941</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1423492012453379</v>
+        <v>0.1297460547946961</v>
       </c>
       <c r="G3" t="n">
-        <v>242.7025850899715</v>
+        <v>229.1975385776941</v>
       </c>
       <c r="H3" t="n">
-        <v>245.5043882209573</v>
+        <v>144.629656515815</v>
       </c>
       <c r="I3" t="n">
-        <v>283.4423603957579</v>
+        <v>144.629656515815</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3027743710562427</v>
+        <v>0.1774249826703231</v>
       </c>
       <c r="K3" t="n">
-        <v>131.6170746632005</v>
+        <v>119.2539037739289</v>
       </c>
       <c r="L3" t="n">
-        <v>138.8183660253818</v>
+        <v>119.2539037739289</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1484725279628364</v>
+        <v>0.1223958910323451</v>
       </c>
     </row>
     <row r="4">
@@ -1174,43 +1097,39 @@
           <t>sim_v2</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>simply</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1043.010096241889</v>
+        <v>2417.698763197545</v>
       </c>
       <c r="E4" t="n">
-        <v>1110.083494735273</v>
+        <v>3918.714650664858</v>
       </c>
       <c r="F4" t="n">
-        <v>1.553094481790185</v>
+        <v>0.6411195581200204</v>
       </c>
       <c r="G4" t="n">
-        <v>380.0201368627239</v>
+        <v>953.9350005730097</v>
       </c>
       <c r="H4" t="n">
-        <v>646.7477601932454</v>
+        <v>1101.033641141734</v>
       </c>
       <c r="I4" t="n">
-        <v>683.0010569681057</v>
+        <v>1886.572670518471</v>
       </c>
       <c r="J4" t="n">
-        <v>2.093144971862683</v>
+        <v>0.5759881680459275</v>
       </c>
       <c r="K4" t="n">
-        <v>532.600342725473</v>
+        <v>1105.790227516862</v>
       </c>
       <c r="L4" t="n">
-        <v>562.8112240933085</v>
+        <v>1831.288483744352</v>
       </c>
       <c r="M4" t="n">
-        <v>1.866833741174933</v>
+        <v>0.4793787730096754</v>
       </c>
     </row>
     <row r="5">
@@ -1219,39 +1138,43 @@
           <t>sim_v2</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>connected</t>
+        </is>
+      </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2837.483473249968</v>
+        <v>3930.335844786559</v>
       </c>
       <c r="E5" t="n">
-        <v>4224.956201567885</v>
+        <v>5057.154262447064</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9895988381250103</v>
+        <v>0.9853676063322273</v>
       </c>
       <c r="G5" t="n">
-        <v>234.0590847484048</v>
+        <v>1490.729573745666</v>
       </c>
       <c r="H5" t="n">
-        <v>1414.283858063291</v>
+        <v>1778.13552103199</v>
       </c>
       <c r="I5" t="n">
-        <v>1985.149711851909</v>
+        <v>2434.076251030682</v>
       </c>
       <c r="J5" t="n">
-        <v>1.158466280664357</v>
+        <v>0.8658199591284536</v>
       </c>
       <c r="K5" t="n">
-        <v>1258.181925873794</v>
+        <v>1794.311861215357</v>
       </c>
       <c r="L5" t="n">
-        <v>1842.24104850642</v>
+        <v>2363.129977663</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9860844252649592</v>
+        <v>0.7199330764070698</v>
       </c>
     </row>
   </sheetData>
@@ -1265,7 +1188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1276,60 +1199,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>solution</t>
+          <t>montant_ventes_mae</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>nombre_hotels</t>
+          <t>montant_ventes_rmse</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>montant_ventes_mae</t>
+          <t>montant_ventes_mape</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>montant_ventes_rmse</t>
+          <t>marge_selon_coef_mae</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>montant_ventes_mape</t>
+          <t>marge_selon_coef_rmse</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>montant_ventes_biais</t>
+          <t>marge_selon_coef_mape</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>marge_selon_coef_mae</t>
+          <t>marge_mae</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>marge_selon_coef_rmse</t>
+          <t>marge_rmse</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
-        <is>
-          <t>marge_selon_coef_mape</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>marge_mae</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>marge_rmse</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
         <is>
           <t>marge_mape</t>
         </is>
@@ -1341,39 +1249,32 @@
           <t>sim_v2</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>2417.698763197545</v>
+      </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>3918.714650664858</v>
       </c>
       <c r="D2" t="n">
-        <v>2837.483473249968</v>
+        <v>0.6411195581200204</v>
       </c>
       <c r="E2" t="n">
-        <v>4224.956201567885</v>
+        <v>1101.033641141734</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9895988381250103</v>
+        <v>1886.572670518471</v>
       </c>
       <c r="G2" t="n">
-        <v>234.0590847484048</v>
+        <v>0.5759881680459275</v>
       </c>
       <c r="H2" t="n">
-        <v>1414.283858063291</v>
+        <v>1105.790227516862</v>
       </c>
       <c r="I2" t="n">
-        <v>1985.149711851909</v>
+        <v>1831.288483744352</v>
       </c>
       <c r="J2" t="n">
-        <v>1.158466280664357</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1258.181925873794</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1842.24104850642</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.9860844252649592</v>
+        <v>0.4793787730096754</v>
       </c>
     </row>
   </sheetData>

--- a/release_1_0_0/data/files/output/sim_v2/eval_sim_v2_loo.xlsx
+++ b/release_1_0_0/data/files/output/sim_v2/eval_sim_v2_loo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,100 +436,110 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>eval_biased</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>n_solution_hotels</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>nombre_guests_par_mois</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>metres_lineaires</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>montant_ventes_par_mois_reel</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>montant_ventes_par_mois_predit</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>montant_ventes_erreur</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>montant_ventes_erreur_absolue</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>montant_ventes_erreur_relative</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>montant_marge_selon_coef_par_mois_reel</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>montant_marge_selon_coef_par_mois_predite</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>montant_marge_selon_coef_erreur</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>montant_marge_selon_coef_erreur_absolue</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>montant_marge_selon_coef_erreur_relative</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>montant_marge_par_mois_reel</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>montant_marge_par_mois_predite</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>montant_marge_erreur</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>montant_marge_erreur_absolue</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>montant_marge_erreur_relative</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>nombre_predicteurs</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>nombre_familles</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>nombre_hotels_apprentissage</t>
         </is>
@@ -551,64 +561,70 @@
           <t>sim_v2</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
         <v>14139.8</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>3432.306971428518</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>11563.90509922685</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>8131.598127798337</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>8131.598127798337</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>2.369134869196733</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>1977.989434346401</v>
       </c>
-      <c r="L2" t="n">
-        <v>6068.039785701236</v>
-      </c>
-      <c r="M2" t="n">
-        <v>4090.050351354835</v>
-      </c>
       <c r="N2" t="n">
-        <v>4090.050351354835</v>
+        <v>6068.039785701235</v>
       </c>
       <c r="O2" t="n">
-        <v>2.067781698088966</v>
+        <v>4090.050351354834</v>
       </c>
       <c r="P2" t="n">
+        <v>4090.050351354834</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.067781698088965</v>
+      </c>
+      <c r="R2" t="n">
         <v>2214.074874999865</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>6058.900290863949</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>3844.825415864083</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>3844.825415864083</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>1.736538117693205</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>9</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>2</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -628,64 +644,70 @@
           <t>sim_v2</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>4815.828</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>6</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>570.2660606060817</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>638.5548036564379</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>68.28874305035617</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>68.28874305035617</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.1197489168087235</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>248.7434418642236</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>274.8754279611125</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>26.13198609688882</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>26.13198609688882</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.1050559801739535</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>233.321212121201</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>260.0828622855092</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>26.76165016430821</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>26.76165016430821</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.1146987447948222</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>10</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>2</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -705,64 +727,70 @@
           <t>sim_v2</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
         <v>33554.88</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>7</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>17096.63041667935</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>13869.445661997</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>-3227.184754682352</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>3227.184754682352</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.1887614504162138</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>8864.534661573482</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>7873.942033712021</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>-990.5926278614606</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>990.5926278614606</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.1117478430261592</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>9167.626249997114</v>
       </c>
-      <c r="Q4" t="n">
-        <v>7771.045887174265</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-1396.58036282285</v>
-      </c>
       <c r="S4" t="n">
-        <v>1396.58036282285</v>
+        <v>7771.045887174266</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1523382743513665</v>
+        <v>-1396.580362822849</v>
       </c>
       <c r="U4" t="n">
+        <v>1396.580362822849</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1523382743513664</v>
+      </c>
+      <c r="W4" t="n">
         <v>9</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>2</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -782,65 +810,71 @@
           <t>sim_v2</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
         <v>18841.68</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>8</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>1766.508730769235</v>
       </c>
-      <c r="G5" t="n">
-        <v>1995.706269346929</v>
-      </c>
-      <c r="H5" t="n">
-        <v>229.1975385776941</v>
-      </c>
       <c r="I5" t="n">
-        <v>229.1975385776941</v>
+        <v>1980.773439202698</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1297460547946961</v>
+        <v>214.2647084334628</v>
       </c>
       <c r="K5" t="n">
+        <v>214.2647084334628</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.1212927537245515</v>
+      </c>
+      <c r="M5" t="n">
         <v>815.1594794547862</v>
       </c>
-      <c r="L5" t="n">
-        <v>959.7891359706011</v>
-      </c>
-      <c r="M5" t="n">
-        <v>144.629656515815</v>
-      </c>
       <c r="N5" t="n">
-        <v>144.629656515815</v>
+        <v>907.0774610810031</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1774249826703231</v>
+        <v>91.91798162621694</v>
       </c>
       <c r="P5" t="n">
+        <v>91.91798162621694</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.112760734485595</v>
+      </c>
+      <c r="R5" t="n">
         <v>974.3293076923151</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1093.583211466244</v>
-      </c>
-      <c r="R5" t="n">
-        <v>119.2539037739289</v>
-      </c>
       <c r="S5" t="n">
-        <v>119.2539037739289</v>
+        <v>1096.883644222921</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1223958910323451</v>
+        <v>122.554336530606</v>
       </c>
       <c r="U5" t="n">
+        <v>122.554336530606</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1257832804197116</v>
+      </c>
+      <c r="W5" t="n">
         <v>12</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>2</v>
       </c>
-      <c r="W5" t="n">
-        <v>2</v>
+      <c r="Y5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -859,64 +893,70 @@
           <t>sim_v2</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
         <v>3520.614999999999</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>2</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>1085.428421052641</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>653.2037691736537</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>-432.2246518789871</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>432.2246518789871</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.3982064993837352</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>607.1911078395337</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>353.4275239598608</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>-253.763583879673</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>253.763583879673</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.4179303362702352</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>522.3989473684123</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>380.8691424092727</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>-141.5298049591396</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>141.5298049591396</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.2709228371766383</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>4</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>2</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1009,41 +1049,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>simply</t>
+          <t>connected</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>68.28874305035617</v>
+        <v>3930.335844786559</v>
       </c>
       <c r="E2" t="n">
-        <v>68.28874305035617</v>
+        <v>5057.154262447064</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1197489168087235</v>
+        <v>0.9853676063322273</v>
       </c>
       <c r="G2" t="n">
-        <v>68.28874305035617</v>
+        <v>1490.729573745666</v>
       </c>
       <c r="H2" t="n">
-        <v>26.13198609688882</v>
+        <v>1778.135521031989</v>
       </c>
       <c r="I2" t="n">
-        <v>26.13198609688882</v>
+        <v>2434.076251030681</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1050559801739535</v>
+        <v>0.8658199591284533</v>
       </c>
       <c r="K2" t="n">
-        <v>26.76165016430821</v>
+        <v>1794.311861215357</v>
       </c>
       <c r="L2" t="n">
-        <v>26.76165016430821</v>
+        <v>2363.129977663</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1146987447948222</v>
+        <v>0.7199330764070697</v>
       </c>
     </row>
     <row r="3">
@@ -1052,43 +1092,39 @@
           <t>sim_v2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>liberty</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>229.1975385776941</v>
+        <v>2414.712197168699</v>
       </c>
       <c r="E3" t="n">
-        <v>229.1975385776941</v>
+        <v>3918.545659304406</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1297460547946961</v>
+        <v>0.6394288979059914</v>
       </c>
       <c r="G3" t="n">
-        <v>229.1975385776941</v>
+        <v>950.9484345441635</v>
       </c>
       <c r="H3" t="n">
-        <v>144.629656515815</v>
+        <v>1090.491306163815</v>
       </c>
       <c r="I3" t="n">
-        <v>144.629656515815</v>
+        <v>1885.911630142745</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1774249826703231</v>
+        <v>0.5630553184089817</v>
       </c>
       <c r="K3" t="n">
-        <v>119.2539037739289</v>
+        <v>1106.450314068197</v>
       </c>
       <c r="L3" t="n">
-        <v>119.2539037739289</v>
+        <v>1831.332063024648</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1223958910323451</v>
+        <v>0.4800562508871487</v>
       </c>
     </row>
     <row r="4">
@@ -1097,39 +1133,43 @@
           <t>sim_v2</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>simply</t>
+        </is>
+      </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2417.698763197545</v>
+        <v>68.28874305035617</v>
       </c>
       <c r="E4" t="n">
-        <v>3918.714650664858</v>
+        <v>68.28874305035617</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6411195581200204</v>
+        <v>0.1197489168087235</v>
       </c>
       <c r="G4" t="n">
-        <v>953.9350005730097</v>
+        <v>68.28874305035617</v>
       </c>
       <c r="H4" t="n">
-        <v>1101.033641141734</v>
+        <v>26.13198609688882</v>
       </c>
       <c r="I4" t="n">
-        <v>1886.572670518471</v>
+        <v>26.13198609688882</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5759881680459275</v>
+        <v>0.1050559801739535</v>
       </c>
       <c r="K4" t="n">
-        <v>1105.790227516862</v>
+        <v>26.76165016430821</v>
       </c>
       <c r="L4" t="n">
-        <v>1831.288483744352</v>
+        <v>26.76165016430821</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4793787730096754</v>
+        <v>0.1146987447948222</v>
       </c>
     </row>
     <row r="5">
@@ -1140,41 +1180,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>connected</t>
+          <t>liberty</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3930.335844786559</v>
+        <v>214.2647084334628</v>
       </c>
       <c r="E5" t="n">
-        <v>5057.154262447064</v>
+        <v>214.2647084334628</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9853676063322273</v>
+        <v>0.1212927537245515</v>
       </c>
       <c r="G5" t="n">
-        <v>1490.729573745666</v>
+        <v>214.2647084334628</v>
       </c>
       <c r="H5" t="n">
-        <v>1778.13552103199</v>
+        <v>91.91798162621694</v>
       </c>
       <c r="I5" t="n">
-        <v>2434.076251030682</v>
+        <v>91.91798162621694</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8658199591284536</v>
+        <v>0.112760734485595</v>
       </c>
       <c r="K5" t="n">
-        <v>1794.311861215357</v>
+        <v>122.554336530606</v>
       </c>
       <c r="L5" t="n">
-        <v>2363.129977663</v>
+        <v>122.554336530606</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7199330764070698</v>
+        <v>0.1257832804197116</v>
       </c>
     </row>
   </sheetData>
@@ -1250,31 +1290,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2417.698763197545</v>
+        <v>2414.712197168699</v>
       </c>
       <c r="C2" t="n">
-        <v>3918.714650664858</v>
+        <v>3918.545659304406</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6411195581200204</v>
+        <v>0.6394288979059914</v>
       </c>
       <c r="E2" t="n">
-        <v>1101.033641141734</v>
+        <v>1090.491306163815</v>
       </c>
       <c r="F2" t="n">
-        <v>1886.572670518471</v>
+        <v>1885.911630142745</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5759881680459275</v>
+        <v>0.5630553184089817</v>
       </c>
       <c r="H2" t="n">
-        <v>1105.790227516862</v>
+        <v>1106.450314068197</v>
       </c>
       <c r="I2" t="n">
-        <v>1831.288483744352</v>
+        <v>1831.332063024648</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4793787730096754</v>
+        <v>0.4800562508871487</v>
       </c>
     </row>
   </sheetData>
